--- a/resources/templates/standard/D1100-02.xlsx
+++ b/resources/templates/standard/D1100-02.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">결
 재</t>
@@ -630,7 +633,9 @@
   <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="2.625" customHeight="1"/>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -663,30 +668,30 @@
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
       <c r="AK1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4"/>
       <c r="AN1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -747,7 +752,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -763,7 +768,7 @@
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
@@ -847,7 +852,7 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -911,69 +916,69 @@
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
       <c r="M6" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" s="10"/>
       <c r="O6" s="10"/>
       <c r="P6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T6" s="10"/>
       <c r="U6" s="10"/>
       <c r="V6" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W6" s="10"/>
       <c r="X6" s="10"/>
       <c r="Y6" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z6" s="10"/>
       <c r="AA6" s="10"/>
       <c r="AB6" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC6" s="10"/>
       <c r="AD6" s="10"/>
       <c r="AE6" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF6" s="10"/>
       <c r="AG6" s="10"/>
       <c r="AH6" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI6" s="10"/>
       <c r="AJ6" s="10"/>
       <c r="AK6" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL6" s="10"/>
       <c r="AM6" s="10"/>
       <c r="AN6" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO6" s="10"/>
       <c r="AP6" s="10"/>
       <c r="AQ6" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR6" s="10"/>
       <c r="AS6" s="10"/>
       <c r="AT6" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU6" s="10"/>
       <c r="AV6" s="10"/>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -984,7 +989,7 @@
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
       <c r="J7" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
@@ -1036,7 +1041,7 @@
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
@@ -1079,7 +1084,7 @@
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -1115,11 +1120,11 @@
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
       <c r="AI9" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ9" s="14"/>
       <c r="AK9" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL9" s="10"/>
       <c r="AM9" s="10"/>
@@ -1127,7 +1132,7 @@
       <c r="AO9" s="10"/>
       <c r="AP9" s="10"/>
       <c r="AQ9" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR9" s="12"/>
       <c r="AS9" s="12"/>
@@ -1173,7 +1178,7 @@
       <c r="AI10" s="14"/>
       <c r="AJ10" s="14"/>
       <c r="AK10" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL10" s="10"/>
       <c r="AM10" s="10"/>
@@ -1181,7 +1186,7 @@
       <c r="AO10" s="10"/>
       <c r="AP10" s="10"/>
       <c r="AQ10" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR10" s="12"/>
       <c r="AS10" s="12"/>
@@ -1227,7 +1232,7 @@
       <c r="AI11" s="14"/>
       <c r="AJ11" s="14"/>
       <c r="AK11" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
@@ -1235,7 +1240,7 @@
       <c r="AO11" s="6"/>
       <c r="AP11" s="6"/>
       <c r="AQ11" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AR11" s="15"/>
       <c r="AS11" s="15"/>
@@ -1245,7 +1250,7 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
